--- a/mode_docx_gen/pmi_ka2/ka_modes/КА_7.xlsx
+++ b/mode_docx_gen/pmi_ka2/ka_modes/КА_7.xlsx
@@ -1122,8 +1122,8 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
+      <c r="H2" t="n">
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1167,8 +1167,8 @@
       <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" t="n">
-        <v>0</v>
+      <c r="W2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -1497,9 +1497,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1507,14 +1507,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1667,9 +1667,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
